--- a/artfynd/A 40263-2025 artfynd.xlsx
+++ b/artfynd/A 40263-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136455480</v>
       </c>
       <c r="B4" t="n">
-        <v>101525</v>
+        <v>101528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40263-2025 artfynd.xlsx
+++ b/artfynd/A 40263-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136455480</v>
       </c>
       <c r="B4" t="n">
-        <v>101528</v>
+        <v>101529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40263-2025 artfynd.xlsx
+++ b/artfynd/A 40263-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455481</v>
       </c>
       <c r="B2" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455483</v>
       </c>
       <c r="B3" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136455480</v>
       </c>
       <c r="B4" t="n">
-        <v>101529</v>
+        <v>101534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136455482</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136455486</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136455484</v>
       </c>
       <c r="B7" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136455485</v>
       </c>
       <c r="B8" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136455487</v>
       </c>
       <c r="B9" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40263-2025 artfynd.xlsx
+++ b/artfynd/A 40263-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136455480</v>
       </c>
       <c r="B4" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40263-2025 artfynd.xlsx
+++ b/artfynd/A 40263-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455481</v>
       </c>
       <c r="B2" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455483</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136455480</v>
       </c>
       <c r="B4" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136455482</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136455486</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136455484</v>
       </c>
       <c r="B7" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136455485</v>
       </c>
       <c r="B8" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136455487</v>
       </c>
       <c r="B9" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40263-2025 artfynd.xlsx
+++ b/artfynd/A 40263-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455481</v>
       </c>
       <c r="B2" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455483</v>
       </c>
       <c r="B3" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136455480</v>
       </c>
       <c r="B4" t="n">
-        <v>101542</v>
+        <v>101544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136455482</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136455486</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136455484</v>
       </c>
       <c r="B7" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136455485</v>
       </c>
       <c r="B8" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136455487</v>
       </c>
       <c r="B9" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40263-2025 artfynd.xlsx
+++ b/artfynd/A 40263-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455481</v>
       </c>
       <c r="B2" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455483</v>
       </c>
       <c r="B3" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136455480</v>
       </c>
       <c r="B4" t="n">
-        <v>101544</v>
+        <v>101545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136455482</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136455486</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136455484</v>
       </c>
       <c r="B7" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136455485</v>
       </c>
       <c r="B8" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>136455487</v>
       </c>
       <c r="B9" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 40263-2025 artfynd.xlsx
+++ b/artfynd/A 40263-2025 artfynd.xlsx
@@ -895,7 +895,7 @@
         <v>136455480</v>
       </c>
       <c r="B4" t="n">
-        <v>101545</v>
+        <v>101551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
